--- a/business_forms/10dlc_internal_messaging_registration_form--business_forms_it_forms_registration_forms.xlsx
+++ b/business_forms/10dlc_internal_messaging_registration_form--business_forms_it_forms_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1639,6 +1639,23 @@
       <c r="C28" t="inlineStr">
         <is>
           <t>I confirm that all information provided above is accurate and complete to the best of my knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>applicant_declaration_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
